--- a/SOT_results/SOT_all_angles_wide.xlsx
+++ b/SOT_results/SOT_all_angles_wide.xlsx
@@ -519,19 +519,19 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>17.47943486872997</v>
+        <v>16.8834155</v>
       </c>
       <c r="C2" t="n">
-        <v>13.17773356095276</v>
+        <v>11.9258011778</v>
       </c>
       <c r="D2" t="n">
-        <v>8.366266926306173</v>
+        <v>7.49381975555</v>
       </c>
       <c r="E2" t="n">
-        <v>3.526342380134457</v>
+        <v>3.610214</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5039641267274426</v>
+        <v>-0.4196801668999999</v>
       </c>
       <c r="G2" t="n">
         <v>-1.941888</v>
@@ -560,19 +560,19 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>17.10272421664234</v>
+        <v>16.8834155</v>
       </c>
       <c r="C3" t="n">
-        <v>12.37553560654939</v>
+        <v>11.9258011778</v>
       </c>
       <c r="D3" t="n">
-        <v>7.783083060659582</v>
+        <v>7.493819755550001</v>
       </c>
       <c r="E3" t="n">
-        <v>3.526342380134457</v>
+        <v>3.610214000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5093984924204307</v>
+        <v>-0.4196801668999992</v>
       </c>
       <c r="G3" t="n">
         <v>-1.951196</v>
@@ -601,19 +601,19 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>16.80418393457441</v>
+        <v>16.8834155</v>
       </c>
       <c r="C4" t="n">
-        <v>11.73979992385841</v>
+        <v>11.9258011778</v>
       </c>
       <c r="D4" t="n">
-        <v>7.32091435164443</v>
+        <v>7.493819755550004</v>
       </c>
       <c r="E4" t="n">
-        <v>3.526342380134457</v>
+        <v>3.610214000000006</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5172874305507262</v>
+        <v>-0.4196801668999955</v>
       </c>
       <c r="G4" t="n">
         <v>-1.9647082</v>
@@ -642,19 +642,19 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>16.83684697057579</v>
+        <v>16.8834155</v>
       </c>
       <c r="C5" t="n">
-        <v>11.80976015985502</v>
+        <v>11.92580117780001</v>
       </c>
       <c r="D5" t="n">
-        <v>7.372657372439897</v>
+        <v>7.493819755550022</v>
       </c>
       <c r="E5" t="n">
-        <v>3.528307906894623</v>
+        <v>3.610214000000031</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5185488521780146</v>
+        <v>-0.4196801668999766</v>
       </c>
       <c r="G5" t="n">
         <v>-1.9684742</v>
@@ -683,19 +683,19 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>16.89469536107498</v>
+        <v>16.88341550000001</v>
       </c>
       <c r="C6" t="n">
-        <v>11.93571315045511</v>
+        <v>11.92580117780004</v>
       </c>
       <c r="D6" t="n">
-        <v>7.47025543984111</v>
+        <v>7.493819755550114</v>
       </c>
       <c r="E6" t="n">
-        <v>3.541733578511137</v>
+        <v>3.610214000000162</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.506655821282364</v>
+        <v>-0.4196801668998785</v>
       </c>
       <c r="G6" t="n">
         <v>-1.9590698</v>
@@ -724,19 +724,19 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>16.89952936182164</v>
+        <v>16.88341550000003</v>
       </c>
       <c r="C7" t="n">
-        <v>11.9478811276776</v>
+        <v>11.92580117780022</v>
       </c>
       <c r="D7" t="n">
-        <v>7.483188588592592</v>
+        <v>7.493819755550594</v>
       </c>
       <c r="E7" t="n">
-        <v>3.550830045967256</v>
+        <v>3.610214000000838</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4932843212412745</v>
+        <v>-0.419680166899369</v>
       </c>
       <c r="G7" t="n">
         <v>-1.943597</v>
@@ -765,19 +765,19 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>16.87219303771848</v>
+        <v>16.88341550000014</v>
       </c>
       <c r="C8" t="n">
-        <v>11.88920660377777</v>
+        <v>11.92580117780111</v>
       </c>
       <c r="D8" t="n">
-        <v>7.439524860393856</v>
+        <v>7.493819755553086</v>
       </c>
       <c r="E8" t="n">
-        <v>3.548585827106368</v>
+        <v>3.610214000004351</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4805465295209971</v>
+        <v>-0.419680166896724</v>
       </c>
       <c r="G8" t="n">
         <v>-1.9199466</v>
@@ -806,19 +806,19 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>16.87124308618445</v>
+        <v>16.88341550000075</v>
       </c>
       <c r="C9" t="n">
-        <v>11.88732083484917</v>
+        <v>11.92580117780578</v>
       </c>
       <c r="D9" t="n">
-        <v>7.43845302201026</v>
+        <v>7.493819755566025</v>
       </c>
       <c r="E9" t="n">
-        <v>3.549251458095975</v>
+        <v>3.610214000022589</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4749331099005129</v>
+        <v>-0.4196801668829919</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9108756</v>
@@ -847,19 +847,19 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>16.87043280080362</v>
+        <v>16.88341550000388</v>
       </c>
       <c r="C10" t="n">
-        <v>11.88537602118982</v>
+        <v>11.92580117782999</v>
       </c>
       <c r="D10" t="n">
-        <v>7.436560836277589</v>
+        <v>7.493819755633199</v>
       </c>
       <c r="E10" t="n">
-        <v>3.548186875626934</v>
+        <v>3.610214000117276</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4667630804392562</v>
+        <v>-0.4196801668116988</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8960124</v>
@@ -888,19 +888,19 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>16.86388013044959</v>
+        <v>16.88341550002017</v>
       </c>
       <c r="C11" t="n">
-        <v>11.87171128689949</v>
+        <v>11.92580117795572</v>
       </c>
       <c r="D11" t="n">
-        <v>7.42725721413388</v>
+        <v>7.493819755981944</v>
       </c>
       <c r="E11" t="n">
-        <v>3.549589879466367</v>
+        <v>3.610214000608861</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4538411263848844</v>
+        <v>-0.4196801664415676</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8750256</v>
@@ -929,19 +929,19 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>16.85969901354604</v>
+        <v>16.88341550010473</v>
       </c>
       <c r="C12" t="n">
-        <v>11.8631872675331</v>
+        <v>11.92580117860846</v>
       </c>
       <c r="D12" t="n">
-        <v>7.421888261011556</v>
+        <v>7.493819757792517</v>
       </c>
       <c r="E12" t="n">
-        <v>3.551432343910026</v>
+        <v>3.610214003161015</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4486411623462382</v>
+        <v>-0.4196801645199623</v>
       </c>
       <c r="G12" t="n">
         <v>-1.867624</v>
@@ -970,19 +970,19 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>16.86149527546073</v>
+        <v>16.88341550054375</v>
       </c>
       <c r="C13" t="n">
-        <v>11.86729511009491</v>
+        <v>11.92580118199728</v>
       </c>
       <c r="D13" t="n">
-        <v>7.425491227348444</v>
+        <v>7.493819767192449</v>
       </c>
       <c r="E13" t="n">
-        <v>3.55280471564356</v>
+        <v>3.610214016411005</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4472393980765773</v>
+        <v>-0.4196801545435873</v>
       </c>
       <c r="G13" t="n">
         <v>-1.866344</v>
@@ -1011,19 +1011,19 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>16.86003709431369</v>
+        <v>16.883415502823</v>
       </c>
       <c r="C14" t="n">
-        <v>11.86399387869406</v>
+        <v>11.92580119959096</v>
       </c>
       <c r="D14" t="n">
-        <v>7.422663686362126</v>
+        <v>7.493819815993961</v>
       </c>
       <c r="E14" t="n">
-        <v>3.551853051525675</v>
+        <v>3.610214085200803</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4476664842523243</v>
+        <v>-0.4196801027493685</v>
       </c>
       <c r="G14" t="n">
         <v>-1.8662982</v>
@@ -1052,19 +1052,19 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>16.85898959816473</v>
+        <v>16.88341551465612</v>
       </c>
       <c r="C15" t="n">
-        <v>11.86162158468165</v>
+        <v>11.92580129093184</v>
       </c>
       <c r="D15" t="n">
-        <v>7.420630092095929</v>
+        <v>7.493820069356063</v>
       </c>
       <c r="E15" t="n">
-        <v>3.551165397453397</v>
+        <v>3.610214442335776</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4492842253968948</v>
+        <v>-0.4196798338500667</v>
       </c>
       <c r="G15" t="n">
         <v>-1.8685074</v>
@@ -1093,19 +1093,19 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>16.85777638701655</v>
+        <v>16.88341557608996</v>
       </c>
       <c r="C16" t="n">
-        <v>11.85911265082287</v>
+        <v>11.92580176514466</v>
       </c>
       <c r="D16" t="n">
-        <v>7.418968786397502</v>
+        <v>7.493821384730269</v>
       </c>
       <c r="E16" t="n">
-        <v>3.551527376848587</v>
+        <v>3.610216296464196</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4658176682244434</v>
+        <v>-0.4196784378117364</v>
       </c>
       <c r="G16" t="n">
         <v>-1.8971216</v>
@@ -1134,19 +1134,19 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>17.04785370805233</v>
+        <v>16.88341589503457</v>
       </c>
       <c r="C17" t="n">
-        <v>12.26374055467733</v>
+        <v>11.92580422709577</v>
       </c>
       <c r="D17" t="n">
-        <v>7.712825155392096</v>
+        <v>7.493828213669662</v>
       </c>
       <c r="E17" t="n">
-        <v>3.55085740797906</v>
+        <v>3.610225922390113</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5258628711528431</v>
+        <v>-0.4196711900938659</v>
       </c>
       <c r="G17" t="n">
         <v>-1.99942</v>
@@ -1175,19 +1175,19 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>17.37541074190787</v>
+        <v>16.88341755087551</v>
       </c>
       <c r="C18" t="n">
-        <v>12.96107597587945</v>
+        <v>11.92581700840688</v>
       </c>
       <c r="D18" t="n">
-        <v>8.219359526865805</v>
+        <v>7.493863665431471</v>
       </c>
       <c r="E18" t="n">
-        <v>3.549930970301326</v>
+        <v>3.610275893693837</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5237722107787219</v>
+        <v>-0.4196335642851063</v>
       </c>
       <c r="G18" t="n">
         <v>-1.9950824</v>
@@ -1216,19 +1216,19 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>17.57173479791449</v>
+        <v>16.88342614694968</v>
       </c>
       <c r="C19" t="n">
-        <v>13.37847210660041</v>
+        <v>11.92588335500683</v>
       </c>
       <c r="D19" t="n">
-        <v>8.521333388293762</v>
+        <v>7.494047667127988</v>
       </c>
       <c r="E19" t="n">
-        <v>3.546668684391467</v>
+        <v>3.610535234866895</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5254910416570647</v>
+        <v>-0.4194382788524134</v>
       </c>
       <c r="G19" t="n">
         <v>-1.9953618</v>
@@ -1257,19 +1257,19 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>17.58320127824558</v>
+        <v>16.88347076067125</v>
       </c>
       <c r="C20" t="n">
-        <v>13.40105990187159</v>
+        <v>11.92622753717346</v>
       </c>
       <c r="D20" t="n">
-        <v>8.533763513239384</v>
+        <v>7.495001526078109</v>
       </c>
       <c r="E20" t="n">
-        <v>3.537786841886478</v>
+        <v>3.61187911836197</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.521234070889021</v>
+        <v>-0.4184259253723688</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9808158</v>
@@ -1298,19 +1298,19 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>17.57560166597336</v>
+        <v>16.88370199342717</v>
       </c>
       <c r="C21" t="n">
-        <v>13.38265288510657</v>
+        <v>11.9280072122887</v>
       </c>
       <c r="D21" t="n">
-        <v>8.515531962378061</v>
+        <v>7.499915681933166</v>
       </c>
       <c r="E21" t="n">
-        <v>3.52699286191265</v>
+        <v>3.618788500603038</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5103016256311537</v>
+        <v>-0.4132104133926276</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9532742</v>
@@ -1339,19 +1339,19 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>17.5380569653794</v>
+        <v>16.88489212332209</v>
       </c>
       <c r="C22" t="n">
-        <v>13.30040617868298</v>
+        <v>11.93705648826432</v>
       </c>
       <c r="D22" t="n">
-        <v>8.450732587372531</v>
+        <v>7.524445369465496</v>
       </c>
       <c r="E22" t="n">
-        <v>3.515848381241267</v>
+        <v>3.652927469688595</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5054368279009545</v>
+        <v>-0.3871764651505178</v>
       </c>
       <c r="G22" t="n">
         <v>-1.935839</v>
@@ -1380,19 +1380,19 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>17.48530971485639</v>
+        <v>16.89080413996444</v>
       </c>
       <c r="C23" t="n">
-        <v>13.16662217718366</v>
+        <v>11.97942850213443</v>
       </c>
       <c r="D23" t="n">
-        <v>8.306671341373042</v>
+        <v>7.629978997786136</v>
       </c>
       <c r="E23" t="n">
-        <v>3.411685606917842</v>
+        <v>3.793447015792268</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5382165682701892</v>
+        <v>-0.275171083350183</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9069046</v>
@@ -1421,19 +1421,19 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>17.10180253087741</v>
+        <v>16.91570608723391</v>
       </c>
       <c r="C24" t="n">
-        <v>12.36418399676562</v>
+        <v>12.1208985354515</v>
       </c>
       <c r="D24" t="n">
-        <v>7.754353945805643</v>
+        <v>7.898741373873175</v>
       </c>
       <c r="E24" t="n">
-        <v>3.480769948424751</v>
+        <v>4.110400030319937</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5142862349093876</v>
+        <v>0.01007290026168889</v>
       </c>
       <c r="G24" t="n">
         <v>-1.9223444</v>
@@ -1462,19 +1462,19 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>17.3916253172168</v>
+        <v>16.97545676069531</v>
       </c>
       <c r="C25" t="n">
-        <v>12.96136472751776</v>
+        <v>12.322440545419</v>
       </c>
       <c r="D25" t="n">
-        <v>8.144894088974961</v>
+        <v>8.147130508230694</v>
       </c>
       <c r="E25" t="n">
-        <v>3.383735311859484</v>
+        <v>4.360323692329992</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5968184289838053</v>
+        <v>0.2736942716812417</v>
       </c>
       <c r="G25" t="n">
         <v>-1.9844484</v>
@@ -1503,19 +1503,19 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>17.59302945243047</v>
+        <v>17.02642929636333</v>
       </c>
       <c r="C26" t="n">
-        <v>13.3846467114349</v>
+        <v>12.42096797572261</v>
       </c>
       <c r="D26" t="n">
-        <v>8.44039026402805</v>
+        <v>8.23466530959443</v>
       </c>
       <c r="E26" t="n">
-        <v>3.356533401192288</v>
+        <v>4.440204079390156</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.7127857314199553</v>
+        <v>0.3665970648816554</v>
       </c>
       <c r="G26" t="n">
         <v>-2.1608592</v>
@@ -1544,19 +1544,19 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>17.40216013562916</v>
+        <v>17.04350629231351</v>
       </c>
       <c r="C27" t="n">
-        <v>12.97819424016057</v>
+        <v>12.44585067323093</v>
       </c>
       <c r="D27" t="n">
-        <v>8.144906434758418</v>
+        <v>8.254291474969587</v>
       </c>
       <c r="E27" t="n">
-        <v>3.356533401192288</v>
+        <v>4.457585312412417</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.9601654374792454</v>
+        <v>0.3874267869437278</v>
       </c>
       <c r="G27" t="n">
         <v>-2.584572</v>
@@ -1585,19 +1585,19 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>17.40497230253911</v>
+        <v>17.0482005</v>
       </c>
       <c r="C28" t="n">
-        <v>13.33508912410903</v>
+        <v>12.4521608222</v>
       </c>
       <c r="D28" t="n">
-        <v>9.169671254739878</v>
+        <v>8.25912824445</v>
       </c>
       <c r="E28" t="n">
-        <v>5.059785401192287</v>
+        <v>4.46184</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7315266803331284</v>
+        <v>0.3925601668999998</v>
       </c>
       <c r="G28" t="n">
         <v>-2.469452</v>
@@ -1626,19 +1626,19 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>17.4892259094535</v>
+        <v>17.0482005</v>
       </c>
       <c r="C29" t="n">
-        <v>13.51450552962682</v>
+        <v>12.4521608222</v>
       </c>
       <c r="D29" t="n">
-        <v>9.300103839809365</v>
+        <v>8.259128244449998</v>
       </c>
       <c r="E29" t="n">
-        <v>5.059785401192287</v>
+        <v>4.461839999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6324362647882658</v>
+        <v>0.3925601668999991</v>
       </c>
       <c r="G29" t="n">
         <v>-2.6391744</v>
@@ -1667,19 +1667,19 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>17.41097185058803</v>
+        <v>17.0482005</v>
       </c>
       <c r="C30" t="n">
-        <v>13.3228734192533</v>
+        <v>12.4521608222</v>
       </c>
       <c r="D30" t="n">
-        <v>9.106285230180562</v>
+        <v>8.259128244449995</v>
       </c>
       <c r="E30" t="n">
-        <v>4.938479458897321</v>
+        <v>4.461839999999994</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5862784234552012</v>
+        <v>0.3925601668999955</v>
       </c>
       <c r="G30" t="n">
         <v>-2.6191516</v>
@@ -1708,19 +1708,19 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>17.64260871989134</v>
+        <v>17.0482005</v>
       </c>
       <c r="C31" t="n">
-        <v>13.71701415982138</v>
+        <v>12.45216082219999</v>
       </c>
       <c r="D31" t="n">
-        <v>9.176631280010083</v>
+        <v>8.259128244449977</v>
       </c>
       <c r="E31" t="n">
-        <v>4.457338101878699</v>
+        <v>4.461839999999969</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3763281536602175</v>
+        <v>0.3925601668999766</v>
       </c>
       <c r="G31" t="n">
         <v>-2.5857612</v>
@@ -1749,19 +1749,19 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>17.65801744366556</v>
+        <v>17.04820049999999</v>
       </c>
       <c r="C32" t="n">
-        <v>13.75444519258381</v>
+        <v>12.45216082219996</v>
       </c>
       <c r="D32" t="n">
-        <v>9.213915598172079</v>
+        <v>8.259128244449885</v>
       </c>
       <c r="E32" t="n">
-        <v>4.479755464467104</v>
+        <v>4.461839999999839</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3796352427385145</v>
+        <v>0.3925601668998784</v>
       </c>
       <c r="G32" t="n">
         <v>-2.5984072</v>
@@ -1790,19 +1790,19 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>17.54056596805999</v>
+        <v>17.04820049999997</v>
       </c>
       <c r="C33" t="n">
-        <v>13.49245611516705</v>
+        <v>12.45216082219979</v>
       </c>
       <c r="D33" t="n">
-        <v>8.997547827513923</v>
+        <v>8.259128244449405</v>
       </c>
       <c r="E33" t="n">
-        <v>4.422099034031906</v>
+        <v>4.461839999999162</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3514905684279914</v>
+        <v>0.392560166899369</v>
       </c>
       <c r="G33" t="n">
         <v>-2.59952</v>
@@ -1831,19 +1831,19 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>17.1117071889081</v>
+        <v>17.04820049999985</v>
       </c>
       <c r="C34" t="n">
-        <v>12.57758148608428</v>
+        <v>12.45216082219889</v>
       </c>
       <c r="D34" t="n">
-        <v>8.328898843788675</v>
+        <v>8.259128244446913</v>
       </c>
       <c r="E34" t="n">
-        <v>4.414195683763694</v>
+        <v>4.461839999995649</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3436730814091082</v>
+        <v>0.3925601668967239</v>
       </c>
       <c r="G34" t="n">
         <v>-2.6064544</v>
@@ -1872,19 +1872,19 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>17.04424400306918</v>
+        <v>17.04820049999925</v>
       </c>
       <c r="C35" t="n">
-        <v>12.43138673690372</v>
+        <v>12.45216082219422</v>
       </c>
       <c r="D35" t="n">
-        <v>8.217093009150146</v>
+        <v>8.259128244433974</v>
       </c>
       <c r="E35" t="n">
-        <v>4.401899796288252</v>
+        <v>4.461839999977411</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3348289715075891</v>
+        <v>0.3925601668829917</v>
       </c>
       <c r="G35" t="n">
         <v>-2.6115594</v>
@@ -1913,19 +1913,19 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>17.04272984461471</v>
+        <v>17.04820049999611</v>
       </c>
       <c r="C36" t="n">
-        <v>12.42793374488073</v>
+        <v>12.45216082217001</v>
       </c>
       <c r="D36" t="n">
-        <v>8.214084133468713</v>
+        <v>8.259128244366801</v>
       </c>
       <c r="E36" t="n">
-        <v>4.400790099868041</v>
+        <v>4.461839999882724</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3331893234998242</v>
+        <v>0.3925601668116988</v>
       </c>
       <c r="G36" t="n">
         <v>-2.6134614</v>
@@ -1954,19 +1954,19 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>17.03027627928823</v>
+        <v>17.04820049997982</v>
       </c>
       <c r="C37" t="n">
-        <v>12.4015762104699</v>
+        <v>12.45216082204428</v>
       </c>
       <c r="D37" t="n">
-        <v>8.195276175100046</v>
+        <v>8.259128244018056</v>
       </c>
       <c r="E37" t="n">
-        <v>4.401576857812344</v>
+        <v>4.461839999391139</v>
       </c>
       <c r="F37" t="n">
-        <v>0.333947974545635</v>
+        <v>0.3925601664415675</v>
       </c>
       <c r="G37" t="n">
         <v>-2.6128046</v>
@@ -1995,19 +1995,19 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>17.02803275314485</v>
+        <v>17.04820049989526</v>
       </c>
       <c r="C38" t="n">
-        <v>12.39686177420067</v>
+        <v>12.45216082139154</v>
       </c>
       <c r="D38" t="n">
-        <v>8.191986499258075</v>
+        <v>8.259128242207483</v>
       </c>
       <c r="E38" t="n">
-        <v>4.401883178871326</v>
+        <v>4.461839996838984</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3344172645781615</v>
+        <v>0.3925601645199622</v>
       </c>
       <c r="G38" t="n">
         <v>-2.612251</v>
@@ -2036,19 +2036,19 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>17.02596713507758</v>
+        <v>17.04820049945624</v>
       </c>
       <c r="C39" t="n">
-        <v>12.3925818051007</v>
+        <v>12.45216081800272</v>
       </c>
       <c r="D39" t="n">
-        <v>8.189133967719497</v>
+        <v>8.25912823280755</v>
       </c>
       <c r="E39" t="n">
-        <v>4.402459449534576</v>
+        <v>4.461839983588995</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3350769404617849</v>
+        <v>0.3925601545435873</v>
       </c>
       <c r="G39" t="n">
         <v>-2.6115918</v>
@@ -2077,19 +2077,19 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>17.02817740737495</v>
+        <v>17.048200497177</v>
       </c>
       <c r="C40" t="n">
-        <v>12.39722479549429</v>
+        <v>12.45216080040904</v>
       </c>
       <c r="D40" t="n">
-        <v>8.192370324294622</v>
+        <v>8.259128184006039</v>
       </c>
       <c r="E40" t="n">
-        <v>4.402150058591342</v>
+        <v>4.461839914799197</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3353766193246073</v>
+        <v>0.3925601027493684</v>
       </c>
       <c r="G40" t="n">
         <v>-2.6108258</v>
@@ -2118,19 +2118,19 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>17.02613672969217</v>
+        <v>17.04820048534388</v>
       </c>
       <c r="C41" t="n">
-        <v>12.39270635773545</v>
+        <v>12.45216070906816</v>
       </c>
       <c r="D41" t="n">
-        <v>8.188708512347855</v>
+        <v>8.259127930643936</v>
       </c>
       <c r="E41" t="n">
-        <v>4.401311045878155</v>
+        <v>4.461839557664224</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3353746917663612</v>
+        <v>0.3925598338500667</v>
       </c>
       <c r="G41" t="n">
         <v>-2.6101438</v>
@@ -2159,19 +2159,19 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>17.02222275201813</v>
+        <v>17.04820042391003</v>
       </c>
       <c r="C42" t="n">
-        <v>12.38430999515282</v>
+        <v>12.45216023485534</v>
       </c>
       <c r="D42" t="n">
-        <v>8.182470105518634</v>
+        <v>8.25912661526973</v>
       </c>
       <c r="E42" t="n">
-        <v>4.401011932373502</v>
+        <v>4.461837703535804</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3355154467042921</v>
+        <v>0.3925584378117362</v>
       </c>
       <c r="G42" t="n">
         <v>-2.6096584</v>
@@ -2200,19 +2200,19 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>17.02068864125606</v>
+        <v>17.04820010496543</v>
       </c>
       <c r="C43" t="n">
-        <v>12.38107977788297</v>
+        <v>12.45215777290423</v>
       </c>
       <c r="D43" t="n">
-        <v>8.180201707416495</v>
+        <v>8.259119786330338</v>
       </c>
       <c r="E43" t="n">
-        <v>4.401189785450231</v>
+        <v>4.461828077609887</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3357487890335164</v>
+        <v>0.3925511900938659</v>
       </c>
       <c r="G43" t="n">
         <v>-2.609404</v>
@@ -2241,19 +2241,19 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>17.01449067859268</v>
+        <v>17.04819844912449</v>
       </c>
       <c r="C44" t="n">
-        <v>12.36793737943099</v>
+        <v>12.45214499159312</v>
       </c>
       <c r="D44" t="n">
-        <v>8.170769637729297</v>
+        <v>8.259084334568529</v>
       </c>
       <c r="E44" t="n">
-        <v>4.401461803889537</v>
+        <v>4.461778106306164</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3433100674593284</v>
+        <v>0.3925135642851064</v>
       </c>
       <c r="G44" t="n">
         <v>-2.5966752</v>
@@ -2282,19 +2282,19 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>17.07331340677963</v>
+        <v>17.04818985305032</v>
       </c>
       <c r="C45" t="n">
-        <v>12.49304017641562</v>
+        <v>12.45207864499317</v>
       </c>
       <c r="D45" t="n">
-        <v>8.261370299826801</v>
+        <v>8.258900332872011</v>
       </c>
       <c r="E45" t="n">
-        <v>4.400689794736963</v>
+        <v>4.461518765133105</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3344592131218199</v>
+        <v>0.3923182788524134</v>
       </c>
       <c r="G45" t="n">
         <v>-2.6112044</v>
@@ -2323,19 +2323,19 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>17.18785129124496</v>
+        <v>17.04814523932875</v>
       </c>
       <c r="C46" t="n">
-        <v>12.73622306873994</v>
+        <v>12.45173446282654</v>
       </c>
       <c r="D46" t="n">
-        <v>8.436582548855364</v>
+        <v>8.257946473921889</v>
       </c>
       <c r="E46" t="n">
-        <v>4.397179048412595</v>
+        <v>4.46017488163803</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3230732241042686</v>
+        <v>0.3913059253723687</v>
       </c>
       <c r="G46" t="n">
         <v>-2.6278388</v>
@@ -2364,19 +2364,19 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>17.27457399622474</v>
+        <v>17.04791400657282</v>
       </c>
       <c r="C47" t="n">
-        <v>12.91827225430441</v>
+        <v>12.4499547877113</v>
       </c>
       <c r="D47" t="n">
-        <v>8.563203879004737</v>
+        <v>8.253032318066834</v>
       </c>
       <c r="E47" t="n">
-        <v>4.384437093408125</v>
+        <v>4.453265499396961</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3198989150893806</v>
+        <v>0.3860904133926276</v>
       </c>
       <c r="G47" t="n">
         <v>-2.6228682</v>
@@ -2405,19 +2405,19 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>17.32125685369913</v>
+        <v>17.04672387667791</v>
       </c>
       <c r="C48" t="n">
-        <v>13.00983049693937</v>
+        <v>12.44090551173568</v>
       </c>
       <c r="D48" t="n">
-        <v>8.612640344994293</v>
+        <v>8.228502630534503</v>
       </c>
       <c r="E48" t="n">
-        <v>4.346324613902167</v>
+        <v>4.419126530311405</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3302405053998392</v>
+        <v>0.3600564651505179</v>
       </c>
       <c r="G48" t="n">
         <v>-2.574025</v>
@@ -2446,19 +2446,19 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>17.11974187233213</v>
+        <v>17.04081186003555</v>
       </c>
       <c r="C49" t="n">
-        <v>12.61395046535296</v>
+        <v>12.39853349786557</v>
       </c>
       <c r="D49" t="n">
-        <v>8.397341929105288</v>
+        <v>8.122969002213864</v>
       </c>
       <c r="E49" t="n">
-        <v>4.507677596674288</v>
+        <v>4.278606984207732</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4050345750712405</v>
+        <v>0.2480510833501829</v>
       </c>
       <c r="G49" t="n">
         <v>-2.5777098</v>
@@ -2487,19 +2487,19 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>17.10853976007673</v>
+        <v>17.01590991276608</v>
       </c>
       <c r="C50" t="n">
-        <v>12.52393337593741</v>
+        <v>12.25706346454851</v>
       </c>
       <c r="D50" t="n">
-        <v>8.187604339112557</v>
+        <v>7.854206626126825</v>
       </c>
       <c r="E50" t="n">
-        <v>4.186534268950545</v>
+        <v>3.961653969680063</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2784337529939935</v>
+        <v>-0.03719290026168892</v>
       </c>
       <c r="G50" t="n">
         <v>-2.5322438</v>
@@ -2528,19 +2528,19 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>17.12700506652899</v>
+        <v>16.95615923930469</v>
       </c>
       <c r="C51" t="n">
-        <v>12.73306025493985</v>
+        <v>12.055521454581</v>
       </c>
       <c r="D51" t="n">
-        <v>8.709972511140437</v>
+        <v>7.605817491769306</v>
       </c>
       <c r="E51" t="n">
-        <v>5.010746402796785</v>
+        <v>3.711730307670008</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7572079601207087</v>
+        <v>-0.3008142716812418</v>
       </c>
       <c r="G51" t="n">
         <v>-2.3854102</v>
@@ -2569,19 +2569,19 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>17.36856543770906</v>
+        <v>16.90518670363667</v>
       </c>
       <c r="C52" t="n">
-        <v>13.29254570896565</v>
+        <v>11.95699402427739</v>
       </c>
       <c r="D52" t="n">
-        <v>9.215041836348</v>
+        <v>7.51828269040557</v>
       </c>
       <c r="E52" t="n">
-        <v>5.229594380134457</v>
+        <v>3.631849920609843</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9956878531071215</v>
+        <v>-0.3937170648816554</v>
       </c>
       <c r="G52" t="n">
         <v>-2.155695</v>
@@ -2610,19 +2610,19 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>17.44820618195268</v>
+        <v>16.88810970768649</v>
       </c>
       <c r="C53" t="n">
-        <v>13.46213911378534</v>
+        <v>11.93211132676907</v>
       </c>
       <c r="D53" t="n">
-        <v>9.338333271919506</v>
+        <v>7.498656525030412</v>
       </c>
       <c r="E53" t="n">
-        <v>5.229594380134457</v>
+        <v>3.614468687587583</v>
       </c>
       <c r="F53" t="n">
-        <v>1.126121971149564</v>
+        <v>-0.4145467869437278</v>
       </c>
       <c r="G53" t="n">
         <v>-1.932287</v>
